--- a/output/Data and Chart Outputs/china_fx_usd_daily.xlsx
+++ b/output/Data and Chart Outputs/china_fx_usd_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$C$2:$C$1440</f>
+              <f>'Chart'!$C$2:$C$1454</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$1440</f>
+              <f>'Chart'!$B$2:$B$1454</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1440"/>
+  <dimension ref="A1:C1454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12302,6 +12302,118 @@
       </c>
       <c r="B1440" t="n">
         <v>6.7038</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1441" t="n">
+        <v>6.7038</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1442" t="n">
+        <v>6.7038</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1443" t="n">
+        <v>6.7038</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1444" t="n">
+        <v>6.7021</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1445" t="n">
+        <v>6.692</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1446" t="n">
+        <v>6.6937</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1447" t="n">
+        <v>6.6926</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1448" t="n">
+        <v>6.6909</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>6.6861</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>6.6806</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>6.6779</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>6.6758</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>6.6745</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>6.6702</v>
       </c>
     </row>
   </sheetData>
@@ -12316,7 +12428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1461"/>
+  <dimension ref="A1:C1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24016,6 +24128,118 @@
         <v>6.7038</v>
       </c>
     </row>
+    <row r="1462">
+      <c r="A1462" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>6.7038</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>6.7038</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>6.7038</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>6.7021</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>6.692</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>6.6937</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>6.6926</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>6.6909</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>6.6861</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>6.6806</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>6.6779</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>6.6758</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>6.6745</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>6.6702</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
